--- a/COST.xlsx
+++ b/COST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="158">
   <si>
     <t>S.No</t>
   </si>
@@ -87,9 +87,6 @@
     <t>HOUSING-GLOVE BOX LHD-MMH</t>
   </si>
   <si>
-    <t>MOULDING ASSY-SIDE SILL,LH / RH OPT</t>
-  </si>
-  <si>
     <t>202</t>
   </si>
   <si>
@@ -138,9 +135,6 @@
     <t>DUCT-DEFROSTER REAR RHD</t>
   </si>
   <si>
-    <t>PNL FR DR MAIN TRIM LH / RH YGN</t>
-  </si>
-  <si>
     <t>TRIM-LUGG SIDE,RH (SPEAKER) WDN</t>
   </si>
   <si>
@@ -150,9 +144,6 @@
     <t>TRIM LUGG SIDE RH  WDN</t>
   </si>
   <si>
-    <t>SIDE SILL LH / RH EMBO-SEMB</t>
-  </si>
-  <si>
     <t>48</t>
   </si>
   <si>
@@ -216,9 +207,6 @@
     <t>MOLDING BACK PANEL</t>
   </si>
   <si>
-    <t>PNL FR DR MAIN TRIM LH / RH NNB</t>
-  </si>
-  <si>
     <t>TRIM LUGG SIDE LH  STD W/O SPKR RDE YGN</t>
   </si>
   <si>
@@ -252,9 +240,6 @@
     <t>SU2i</t>
   </si>
   <si>
-    <t>SU2i FL</t>
-  </si>
-  <si>
     <t>Ai3</t>
   </si>
   <si>
@@ -309,9 +294,6 @@
     <t>DR ASSY-PASSENGER AIRBAG LHD</t>
   </si>
   <si>
-    <t>201</t>
-  </si>
-  <si>
     <t>PNL ASSY-CRASH PAD LWR D/SIDE +SSB LHD MMH</t>
   </si>
   <si>
@@ -366,23 +348,176 @@
     <t>340</t>
   </si>
   <si>
-    <t>SU2I FL</t>
-  </si>
-  <si>
     <t>TRIM LUGGAGE SIDE-LH NNB</t>
+  </si>
+  <si>
+    <t>SU2iFL</t>
+  </si>
+  <si>
+    <t>MOLDING ASSY SIDE SILL LH/RH OPT</t>
+  </si>
+  <si>
+    <t>SIDE SILL LH/RH-EMBO-SEMBL</t>
+  </si>
+  <si>
+    <t>SU2iPE</t>
+  </si>
+  <si>
+    <t>PNL FR DR MAIN TRIM LH/RH NNB</t>
+  </si>
+  <si>
+    <t>PNL FR DR MAIN TRIM LH/RH YGN</t>
+  </si>
+  <si>
+    <t>HOUSING-GLOVE BOX LHD-NNB</t>
+  </si>
+  <si>
+    <t>CUP HOLDER ASSY-LUGGAGE SD, LH/RH WDN</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>CUP HOLDER ASSY-LUGGAGE SD, LH/RH YGN</t>
+  </si>
+  <si>
+    <t>SU2IEV</t>
+  </si>
+  <si>
+    <t>HOUSING-ACTIVE AIR LH NNB</t>
+  </si>
+  <si>
+    <t>Ai3PE</t>
+  </si>
+  <si>
+    <t>COVER-GLOVE ASSY BOX LHD MMH</t>
+  </si>
+  <si>
+    <t>PNL ASSY-CRASH PAD LWR D/SIDE LHD NNB</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>SU2IPE</t>
+  </si>
+  <si>
+    <t>S/COVER FRT CUSH OTR RH MNL H/ADJ RHD</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>S/COVER FRT SEAT OTR LH/RH MNL WDN</t>
+  </si>
+  <si>
+    <t>SU2i/Bi3</t>
+  </si>
+  <si>
+    <t>S/COVER FRT CUSH OTR RH MNL H/ADJ RHD NNB</t>
+  </si>
+  <si>
+    <t>DUCT-DEFROSTER FRONT LHD</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR LH STD T9Y</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>BI3PE</t>
+  </si>
+  <si>
+    <t>S/COVER-FR SEAT OTR RH PWR NNB</t>
+  </si>
+  <si>
+    <t>S/COVER-FR SEAT OTR RH PWR YGN</t>
+  </si>
+  <si>
+    <t>Ai3/MS1PE</t>
+  </si>
+  <si>
+    <t>LEVER ASSY FRT SEAT H/ADJ LH AI3</t>
+  </si>
+  <si>
+    <t>PNL ASSY-CRASH PAD LWR D/SIDE +SSB LHD MMH LJMM</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>PNL ASSY-CRASH PAD LWR D/SIDE +SSB NNB LHD LJNN</t>
+  </si>
+  <si>
+    <t>TRIM LUGG TRAY COVER LH/RH YGN</t>
+  </si>
+  <si>
+    <t>S/COVER FRT SEAT OTR LH MNL H/ADJ LHD NNB</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>S/COVER FRT CUSH OTR RH MNL</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>QXi</t>
+  </si>
+  <si>
+    <t>SIDE SILL LH/RH-QXIL/QXIR</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>MOULDING ASSY-SIDE SILL,LH/RH</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>SIDE SILL LH/RH-EMBO-SEMBL/SEMBR</t>
+  </si>
+  <si>
+    <t>212</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -445,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -456,17 +591,20 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -593,8 +731,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D72" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D96" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D96"/>
   <sortState ref="A2:D56">
     <sortCondition ref="C1:C56"/>
   </sortState>
@@ -872,7 +1010,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D280"/>
   <sheetFormatPr defaultColWidth="52.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -901,13 +1039,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -915,13 +1053,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -929,10 +1067,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>13</v>
@@ -943,10 +1081,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -957,7 +1095,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>6</v>
@@ -971,10 +1109,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
@@ -985,10 +1123,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>13</v>
@@ -999,13 +1137,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1013,13 +1151,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1027,13 +1165,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1041,13 +1179,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1055,13 +1193,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1069,13 +1207,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>44</v>
+      <c r="D14" s="3">
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1083,13 +1221,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1097,13 +1235,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1111,13 +1249,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1125,13 +1263,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>14</v>
+      <c r="D18" s="3">
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1139,7 +1277,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>20</v>
@@ -1153,13 +1291,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1167,10 +1305,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>14</v>
@@ -1181,7 +1319,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>8</v>
@@ -1195,13 +1333,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1209,13 +1347,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1223,10 +1361,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>15</v>
@@ -1237,13 +1375,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1251,13 +1389,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1265,10 +1403,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>12</v>
@@ -1279,10 +1417,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>12</v>
@@ -1293,10 +1431,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>12</v>
@@ -1307,10 +1445,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>12</v>
@@ -1321,10 +1459,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>12</v>
@@ -1335,13 +1473,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1349,13 +1487,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>50</v>
+        <v>115</v>
+      </c>
+      <c r="D34" s="3">
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1363,10 +1501,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>12</v>
@@ -1377,13 +1515,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1391,13 +1529,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,13 +1543,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1419,13 +1557,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1433,13 +1571,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1447,13 +1585,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1461,13 +1599,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1475,10 +1613,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>17</v>
@@ -1489,13 +1627,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1503,13 +1641,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1517,13 +1655,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1531,13 +1669,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1545,13 +1683,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1559,10 +1697,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>16</v>
@@ -1573,13 +1711,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1587,13 +1725,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>28</v>
+      <c r="D51" s="3">
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1601,13 +1739,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>16</v>
+      <c r="D52" s="3">
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,13 +1753,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1629,13 +1767,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1643,390 +1781,588 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="3"/>
+      <c r="B56" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="5">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="D59" s="5">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D60" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="5">
-        <v>57</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" s="6" t="s">
+      <c r="D61" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D62" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D67" s="5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
-        <v>58</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="5">
-        <v>59</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
-        <v>60</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="5">
-        <v>61</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="5">
-        <v>62</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="5">
-        <v>63</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
-        <v>64</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="5">
-        <v>65</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="5">
-        <v>66</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="5">
-        <v>67</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C68" s="6" t="s">
+      <c r="B71" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D71" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="5">
-        <v>68</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="5">
-        <v>69</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="5">
-        <v>70</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="5">
-        <v>71</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>116</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-      <c r="B73"/>
-      <c r="C73"/>
-      <c r="D73"/>
+      <c r="A73" s="8">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-      <c r="B74"/>
-      <c r="C74"/>
-      <c r="D74"/>
+      <c r="A74" s="8">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-      <c r="B75"/>
-      <c r="C75"/>
-      <c r="D75"/>
+      <c r="A75" s="8">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76"/>
-      <c r="B76"/>
-      <c r="C76"/>
-      <c r="D76"/>
+      <c r="A76" s="8">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77"/>
-      <c r="B77"/>
-      <c r="C77"/>
-      <c r="D77"/>
+      <c r="A77" s="8">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
+      <c r="A78" s="8">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79"/>
-      <c r="B79"/>
-      <c r="C79"/>
-      <c r="D79"/>
+      <c r="A79" s="8">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80"/>
-      <c r="B80"/>
-      <c r="C80"/>
-      <c r="D80"/>
+      <c r="A80" s="8">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-      <c r="B81"/>
-      <c r="C81"/>
-      <c r="D81"/>
+      <c r="A81" s="8">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6">
+        <v>0</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82"/>
-      <c r="B82"/>
-      <c r="C82"/>
-      <c r="D82"/>
+      <c r="A82" s="8">
+        <v>81</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83"/>
-      <c r="B83"/>
-      <c r="C83"/>
-      <c r="D83"/>
+      <c r="A83" s="8">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84"/>
-      <c r="B84"/>
-      <c r="C84"/>
-      <c r="D84"/>
+      <c r="A84" s="8">
+        <v>83</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85"/>
-      <c r="B85"/>
-      <c r="C85"/>
-      <c r="D85"/>
+      <c r="A85" s="8">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86"/>
-      <c r="B86"/>
-      <c r="C86"/>
-      <c r="D86"/>
+      <c r="A86" s="8">
+        <v>85</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87"/>
-      <c r="B87"/>
-      <c r="C87"/>
-      <c r="D87"/>
+      <c r="A87" s="8">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88"/>
-      <c r="B88"/>
-      <c r="C88"/>
-      <c r="D88"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89"/>
-      <c r="B89"/>
-      <c r="C89"/>
-      <c r="D89"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90"/>
-      <c r="B90"/>
-      <c r="C90"/>
-      <c r="D90"/>
+      <c r="A88" s="8">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D88" s="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="8">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91"/>
-      <c r="B91"/>
-      <c r="C91"/>
-      <c r="D91"/>
+      <c r="A91" s="8">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92"/>
-      <c r="B92"/>
-      <c r="C92"/>
-      <c r="D92"/>
+      <c r="A92" s="8">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93"/>
-      <c r="B93"/>
-      <c r="C93"/>
-      <c r="D93"/>
+      <c r="A93" s="8">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94"/>
-      <c r="B94"/>
-      <c r="C94"/>
-      <c r="D94"/>
+      <c r="A94" s="8">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95"/>
-      <c r="B95"/>
-      <c r="C95"/>
-      <c r="D95"/>
+      <c r="A95" s="8">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-      <c r="B96"/>
-      <c r="C96"/>
-      <c r="D96"/>
+      <c r="A96" s="8">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97"/>
@@ -3131,12 +3467,6 @@
       <c r="B280"/>
       <c r="C280"/>
       <c r="D280"/>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281"/>
-      <c r="B281"/>
-      <c r="C281"/>
-      <c r="D281"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/COST.xlsx
+++ b/COST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="152">
   <si>
     <t>S.No</t>
   </si>
@@ -453,9 +453,6 @@
     <t>PNL ASSY-CRASH PAD LWR D/SIDE +SSB LHD MMH LJMM</t>
   </si>
   <si>
-    <t>91</t>
-  </si>
-  <si>
     <t>PNL ASSY-CRASH PAD LWR D/SIDE +SSB NNB LHD LJNN</t>
   </si>
   <si>
@@ -465,34 +462,19 @@
     <t>S/COVER FRT SEAT OTR LH MNL H/ADJ LHD NNB</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
     <t>S/COVER FRT CUSH OTR RH MNL</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>QXi</t>
   </si>
   <si>
     <t>SIDE SILL LH/RH-QXIL/QXIR</t>
   </si>
   <si>
-    <t>207</t>
-  </si>
-  <si>
     <t>MOULDING ASSY-SIDE SILL,LH/RH</t>
   </si>
   <si>
-    <t>195</t>
-  </si>
-  <si>
     <t>SIDE SILL LH/RH-EMBO-SEMBL/SEMBR</t>
-  </si>
-  <si>
-    <t>212</t>
   </si>
 </sst>
 </file>
@@ -731,8 +713,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D96" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D96"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D97" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D97"/>
   <sortState ref="A2:D56">
     <sortCondition ref="C1:C56"/>
   </sortState>
@@ -2262,8 +2244,8 @@
       <c r="C89" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D89" s="5" t="s">
-        <v>144</v>
+      <c r="D89" s="5">
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
@@ -2274,10 +2256,10 @@
         <v>122</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D90" s="5" t="s">
         <v>144</v>
+      </c>
+      <c r="D90" s="5">
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2288,10 +2270,10 @@
         <v>113</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>66</v>
+        <v>145</v>
+      </c>
+      <c r="D91" s="5">
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,10 +2284,10 @@
         <v>131</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
+      </c>
+      <c r="D92" s="5">
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2316,10 +2298,10 @@
         <v>131</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
+      </c>
+      <c r="D93" s="5">
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2327,13 +2309,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
+      </c>
+      <c r="D94" s="5">
+        <v>207</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2344,10 +2326,10 @@
         <v>113</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
+      </c>
+      <c r="D95" s="5">
+        <v>195</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2358,17 +2340,17 @@
         <v>72</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
+      </c>
+      <c r="D96" s="5">
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-      <c r="B97"/>
-      <c r="C97"/>
-      <c r="D97"/>
+      <c r="A97" s="8"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="5"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98"/>

--- a/COST.xlsx
+++ b/COST.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{128C6530-8463-4D0F-83BE-57B4B8047B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38C798D6-8780-4836-BB4A-1EF7E31E707D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COST" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="522">
   <si>
     <t>S.No</t>
   </si>
@@ -982,9 +982,6 @@
     <t>SHROUD STRG/COL LWR + KEY</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
     <t>HOUSING S A STD SU2i R C LH HOUSING S A STD SU2I R C RH</t>
   </si>
   <si>
@@ -1340,13 +1337,262 @@
   </si>
   <si>
     <t>415</t>
+  </si>
+  <si>
+    <t>SHIELD  COVER  FRT  SEAT  INR  RH  PWR NNB</t>
+  </si>
+  <si>
+    <t>S/COVER FRT SEAT OTR LH MNL H/ADJ LHD; S/COVER FRT CUSH OTR RH MNL  YGN</t>
+  </si>
+  <si>
+    <t>PS7IRDE</t>
+  </si>
+  <si>
+    <t>PNL ASSY-CRASH PAD LWR D/SIDE TTX RHD LHTX</t>
+  </si>
+  <si>
+    <t>COVER-GLOVE BOX LHD TTX</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR LH H/ADJ TTX</t>
+  </si>
+  <si>
+    <t>TRIM LUGG TRAY COVERLH/RH NNB</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FR SEAT INR LH PWR NNB</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FR SEAT INR LH PWR YGN</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR RH STD TTX</t>
+  </si>
+  <si>
+    <t>PNL ASSY-CRASH PAD LWR D/SIDE LHD UMG</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>KNOB FR SEAT RECL RH NNB</t>
+  </si>
+  <si>
+    <t>PNL ASSY-CRASH PAD LWR D SIDE YPK RHD LHYP</t>
+  </si>
+  <si>
+    <t>S/COVER FRT CUSH OTR RH MNL UMG</t>
+  </si>
+  <si>
+    <t>KNOB FR SEAT RECL LH NNB</t>
+  </si>
+  <si>
+    <t>LQ2I HOUSING124W</t>
+  </si>
+  <si>
+    <t>KNOB ASSY FRT SEAT H /ADJ RH NNB</t>
+  </si>
+  <si>
+    <t>COVER COOL BOX LHD</t>
+  </si>
+  <si>
+    <t>AI3/SUVE</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR STD LH/H.RH NNB</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR STD LH/H.RH NBY</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR HEIGHT LH NNB</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR HEIGHT LH T9Y</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR STD LH T9Y</t>
+  </si>
+  <si>
+    <t>SU2I/BI3</t>
+  </si>
+  <si>
+    <t>S/COVER FRT SEAT OTR LH H.ADJ/RH MNL NNB</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>S/COVER FRT SEAT OTR LH MNL/RH H.ADJ YGN</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>HOUSING-GLOVE BOX LHD MMH</t>
+  </si>
+  <si>
+    <t>DUCT DEFROSTER REAR LHD</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>HOUSING-GLOVE BOX RHD #3 MMH</t>
+  </si>
+  <si>
+    <t>HOUSING-GLOVE BOX RHD #3 TTX</t>
+  </si>
+  <si>
+    <t>HOUSING-GLOVE BOX RHD #3 YPK</t>
+  </si>
+  <si>
+    <t>TRIM-LUGG SIDE  SPEAKER RH YGN</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>TRIM-LUGG SIDE W/O SPKR RH YGN</t>
+  </si>
+  <si>
+    <t>TRIM LUGGAGE SIDE LH NNB</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>TRIM LUGGAGE SIDE LH YGN</t>
+  </si>
+  <si>
+    <t>S/COVER FRT CUSH OTR RH MNL H/ADJ RHD YGN</t>
+  </si>
+  <si>
+    <t>SHIELD  COVER  FRT  SEAT  INR  RH  PWR WDN</t>
+  </si>
+  <si>
+    <t>Santhosh</t>
+  </si>
+  <si>
+    <t>994654354654</t>
+  </si>
+  <si>
+    <t>LEVER ASSY FRT SEAT H/ADJ RH NBY</t>
+  </si>
+  <si>
+    <t>Ai3SUV</t>
+  </si>
+  <si>
+    <t>PNL-ASSY C/PAD LWR DRIVER SIDE RHD TTX</t>
+  </si>
+  <si>
+    <t>PNL-ASSY C/PAD LWR DRIVER SIDE RHD YPK</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>S/COVER FRT SEAT OTR LH MNL/RH H.ADJ WDN</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>SHIELD COVER -FR SEAT OTR PWR RH YGN</t>
+  </si>
+  <si>
+    <t>HOUSING REAR COMBI OPT LH/RH</t>
+  </si>
+  <si>
+    <t>SIDE SILL LH/RH</t>
+  </si>
+  <si>
+    <t>TRIM-LUGG SIDE LH SUB WOOFER RDE WDN</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>PNL C/PAD LWR RHD NO HOLE T9Y</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>DR ASSY-PASSENGER AIRBAG RHD #1</t>
+  </si>
+  <si>
+    <t>PNL ASSY-CRASH PAD LWR D/SIDE YPK RHD      LLYP</t>
+  </si>
+  <si>
+    <t>Ai3/SUVPE</t>
+  </si>
+  <si>
+    <t>PNL ASSY-CRASH PAD LWR D/SIDE MMH RHD LHTX</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR LH STD/ RH       H/ADJ T9Y</t>
+  </si>
+  <si>
+    <t>S/COVER FRT SEAT OTR LH H.ADJ/RH MNL        NNB</t>
+  </si>
+  <si>
+    <t>S/COVER OTR FRT SEAT OTR LH MNL/RH.H ADJ  NNB</t>
+  </si>
+  <si>
+    <t>LEVER ASSY-FR SEAT HGT_ADJM, RH</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR LH STD QXI</t>
+  </si>
+  <si>
+    <t>SU2i/BN7i/Bi3</t>
+  </si>
+  <si>
+    <t>PNL ASSY-CRASH PAD LWR D/SIDE +SSB NNB LHD NNB</t>
+  </si>
+  <si>
+    <t>S/COVER FRT SEAT OTR LH MNL; S/COVER FRT SEAT OTR LH MNL H/ADJ LHD YGN</t>
+  </si>
+  <si>
+    <t>HOUSING BN7I DRL PSTN RH</t>
+  </si>
+  <si>
+    <t>SHIELD COVER-2ND CUSH OTR LH; SHIELD COVER 2ND CUSH OTR RH WDN</t>
+  </si>
+  <si>
+    <t>HOUSING BN7I DRL PSTN LH</t>
+  </si>
+  <si>
+    <t>KNOB ASSY FRT SEAT H /ADJ LH YGN</t>
+  </si>
+  <si>
+    <t>PNL FR DR MAIN TRIM LH NNB</t>
+  </si>
+  <si>
+    <t>PS7IFL</t>
+  </si>
+  <si>
+    <t>HOUSING 72W</t>
+  </si>
+  <si>
+    <t>SHILD CVR INR LH HT ADJ; SHILD CVR INR  RH NNB</t>
+  </si>
+  <si>
+    <t>GSPE MOULDING ASSY-SIDE SILL,LH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1471,6 +1717,62 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1520,7 +1822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1586,6 +1888,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1744,8 +2070,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:D437" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D437" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:D528" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D528" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D56">
     <sortCondition ref="C1:C56"/>
   </sortState>
@@ -2022,7 +2348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D437"/>
+  <dimension ref="A1:D528"/>
   <sheetFormatPr defaultColWidth="52.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -2084,8 +2410,8 @@
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
+      <c r="D4" s="3">
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2224,8 +2550,8 @@
       <c r="C14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
+      <c r="D14" s="3">
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2644,8 +2970,8 @@
       <c r="C44" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>67</v>
+      <c r="D44" s="3">
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2855,7 +3181,7 @@
         <v>87</v>
       </c>
       <c r="D59" s="5">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2981,7 +3307,7 @@
         <v>101</v>
       </c>
       <c r="D68" s="5">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3092,8 +3418,8 @@
       <c r="C76" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="5">
-        <v>82</v>
+      <c r="D76" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3120,8 +3446,8 @@
       <c r="C78" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D78" s="5" t="s">
-        <v>45</v>
+      <c r="D78" s="5">
+        <v>82</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -5011,7 +5337,7 @@
         <v>250</v>
       </c>
       <c r="D213" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -5248,8 +5574,8 @@
       <c r="C230" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D230" s="5" t="s">
-        <v>267</v>
+      <c r="D230" s="5">
+        <v>59</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5668,8 +5994,8 @@
       <c r="C260" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="D260" s="5" t="s">
-        <v>163</v>
+      <c r="D260" s="5">
+        <v>81</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5780,8 +6106,8 @@
       <c r="C268" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D268" s="5" t="s">
-        <v>296</v>
+      <c r="D268" s="5">
+        <v>130</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -5808,8 +6134,8 @@
       <c r="C270" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D270" s="5">
-        <v>207</v>
+      <c r="D270" s="5" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5990,8 +6316,8 @@
       <c r="C283" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="D283" s="10" t="s">
-        <v>67</v>
+      <c r="D283" s="10">
+        <v>233</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -6200,8 +6526,8 @@
       <c r="C298" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D298" s="5" t="s">
-        <v>320</v>
+      <c r="D298" s="5">
+        <v>51</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6212,7 +6538,7 @@
         <v>93</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D299" s="5" t="s">
         <v>61</v>
@@ -6226,7 +6552,7 @@
         <v>93</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D300" s="5" t="s">
         <v>61</v>
@@ -6240,7 +6566,7 @@
         <v>83</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D301" s="5">
         <v>123</v>
@@ -6251,7 +6577,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>47</v>
@@ -6265,7 +6591,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>317</v>
@@ -6282,7 +6608,7 @@
         <v>240</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D304" s="5">
         <v>67</v>
@@ -6296,7 +6622,7 @@
         <v>50</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D305" s="5">
         <v>84</v>
@@ -6310,7 +6636,7 @@
         <v>240</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D306" s="5">
         <v>67</v>
@@ -6324,7 +6650,7 @@
         <v>240</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D307" s="5">
         <v>67</v>
@@ -6338,7 +6664,7 @@
         <v>240</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D308" s="5">
         <v>67</v>
@@ -6349,10 +6675,10 @@
         <v>308</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D309" s="5">
         <v>82</v>
@@ -6366,7 +6692,7 @@
         <v>50</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D310" s="5">
         <v>13</v>
@@ -6380,7 +6706,7 @@
         <v>240</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D311" s="5">
         <v>67</v>
@@ -6394,7 +6720,7 @@
         <v>50</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D312" s="5">
         <v>323</v>
@@ -6408,7 +6734,7 @@
         <v>240</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D313" s="5">
         <v>19</v>
@@ -6422,7 +6748,7 @@
         <v>240</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D314" s="5">
         <v>19</v>
@@ -6436,7 +6762,7 @@
         <v>13</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D315" s="5">
         <v>70</v>
@@ -6450,7 +6776,7 @@
         <v>4</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D316" s="5">
         <v>211</v>
@@ -6461,10 +6787,10 @@
         <v>316</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D317" s="5">
         <v>67</v>
@@ -6475,7 +6801,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>24</v>
@@ -6492,10 +6818,10 @@
         <v>4</v>
       </c>
       <c r="C319" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="D319" s="13" t="s">
         <v>340</v>
-      </c>
-      <c r="D319" s="13" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6506,7 +6832,7 @@
         <v>83</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D320" s="5" t="s">
         <v>56</v>
@@ -6520,7 +6846,7 @@
         <v>83</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D321" s="5" t="s">
         <v>56</v>
@@ -6531,7 +6857,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>188</v>
@@ -6548,7 +6874,7 @@
         <v>62</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D323" s="5" t="s">
         <v>56</v>
@@ -6576,7 +6902,7 @@
         <v>93</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D325" s="5" t="s">
         <v>61</v>
@@ -6590,7 +6916,7 @@
         <v>121</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D326" s="5">
         <v>67</v>
@@ -6604,7 +6930,7 @@
         <v>113</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D327" s="5">
         <v>14</v>
@@ -6615,10 +6941,10 @@
         <v>327</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D328" s="5">
         <v>82</v>
@@ -6646,7 +6972,7 @@
         <v>4</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D330" s="5" t="s">
         <v>119</v>
@@ -6674,7 +7000,7 @@
         <v>83</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D332" s="5" t="s">
         <v>36</v>
@@ -6730,7 +7056,7 @@
         <v>281</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D336" s="5" t="s">
         <v>61</v>
@@ -6744,7 +7070,7 @@
         <v>93</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D337" s="5" t="s">
         <v>61</v>
@@ -6758,10 +7084,10 @@
         <v>91</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="D338" s="5" t="s">
-        <v>260</v>
+        <v>353</v>
+      </c>
+      <c r="D338" s="5">
+        <v>124</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -6772,7 +7098,7 @@
         <v>103</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D339" s="5">
         <v>340</v>
@@ -6783,7 +7109,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>82</v>
@@ -6800,7 +7126,7 @@
         <v>113</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D341" s="5" t="s">
         <v>161</v>
@@ -6814,7 +7140,7 @@
         <v>307</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D342" s="5" t="s">
         <v>119</v>
@@ -6828,7 +7154,7 @@
         <v>307</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D343" s="5" t="s">
         <v>119</v>
@@ -6839,10 +7165,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D344" s="5">
         <v>67</v>
@@ -6884,7 +7210,7 @@
         <v>221</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D347" s="5">
         <v>13</v>
@@ -6895,10 +7221,10 @@
         <v>347</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D348" s="5">
         <v>123</v>
@@ -6926,7 +7252,7 @@
         <v>83</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D350" s="5">
         <v>45</v>
@@ -6951,7 +7277,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C352" s="15" t="s">
         <v>315</v>
@@ -6968,7 +7294,7 @@
         <v>113</v>
       </c>
       <c r="C353" s="15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D353" s="16" t="s">
         <v>163</v>
@@ -6982,7 +7308,7 @@
         <v>248</v>
       </c>
       <c r="C354" s="15" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D354" s="16">
         <v>67</v>
@@ -6996,10 +7322,10 @@
         <v>135</v>
       </c>
       <c r="C355" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="D355" s="16" t="s">
         <v>365</v>
-      </c>
-      <c r="D355" s="16" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -7010,7 +7336,7 @@
         <v>4</v>
       </c>
       <c r="C356" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D356" s="16" t="s">
         <v>195</v>
@@ -7021,10 +7347,10 @@
         <v>356</v>
       </c>
       <c r="B357" s="15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C357" s="15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D357" s="16" t="s">
         <v>163</v>
@@ -7052,7 +7378,7 @@
         <v>7</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D359" s="5">
         <v>81</v>
@@ -7066,7 +7392,7 @@
         <v>141</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D360" s="5">
         <v>81</v>
@@ -7080,7 +7406,7 @@
         <v>240</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D361" s="5">
         <v>67</v>
@@ -7094,7 +7420,7 @@
         <v>7</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D362" s="5" t="s">
         <v>163</v>
@@ -7108,7 +7434,7 @@
         <v>4</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D363" s="5">
         <v>313</v>
@@ -7119,10 +7445,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D364" s="5">
         <v>22</v>
@@ -7150,7 +7476,7 @@
         <v>113</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D366" s="5">
         <v>81</v>
@@ -7161,10 +7487,10 @@
         <v>366</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D367" s="5">
         <v>81</v>
@@ -7178,7 +7504,7 @@
         <v>4</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D368" s="5">
         <v>302</v>
@@ -7192,7 +7518,7 @@
         <v>4</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D369" s="5">
         <v>128</v>
@@ -7220,7 +7546,7 @@
         <v>246</v>
       </c>
       <c r="C371" s="18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D371" s="19">
         <v>67</v>
@@ -7231,7 +7557,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>316</v>
@@ -7248,7 +7574,7 @@
         <v>240</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D373" s="5">
         <v>67</v>
@@ -7259,10 +7585,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D374" s="5">
         <v>67</v>
@@ -7290,10 +7616,10 @@
         <v>240</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="D376" s="5" t="s">
-        <v>56</v>
+        <v>378</v>
+      </c>
+      <c r="D376" s="5">
+        <v>67</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -7304,7 +7630,7 @@
         <v>13</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D377" s="5">
         <v>121</v>
@@ -7318,7 +7644,7 @@
         <v>113</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D378" s="5">
         <v>22</v>
@@ -7346,7 +7672,7 @@
         <v>13</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D380" s="5">
         <v>124</v>
@@ -7360,7 +7686,7 @@
         <v>37</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D381" s="5">
         <v>382</v>
@@ -7402,7 +7728,7 @@
         <v>227</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D384" s="5">
         <v>369</v>
@@ -7430,7 +7756,7 @@
         <v>240</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D386" s="5">
         <v>67</v>
@@ -7444,7 +7770,7 @@
         <v>83</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D387" s="5">
         <v>45</v>
@@ -7483,13 +7809,13 @@
         <v>389</v>
       </c>
       <c r="B390" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C390" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="C390" s="4" t="s">
+      <c r="D390" s="5" t="s">
         <v>387</v>
-      </c>
-      <c r="D390" s="5" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -7497,13 +7823,13 @@
         <v>390</v>
       </c>
       <c r="B391" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C391" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="C391" s="4" t="s">
+      <c r="D391" s="5" t="s">
         <v>390</v>
-      </c>
-      <c r="D391" s="5" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -7514,10 +7840,10 @@
         <v>111</v>
       </c>
       <c r="C392" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D392" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="D392" s="5" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -7528,10 +7854,10 @@
         <v>83</v>
       </c>
       <c r="C393" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D393" s="5" t="s">
         <v>394</v>
-      </c>
-      <c r="D393" s="5" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -7542,10 +7868,10 @@
         <v>83</v>
       </c>
       <c r="C394" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D394" s="5" t="s">
         <v>396</v>
-      </c>
-      <c r="D394" s="5" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -7553,10 +7879,10 @@
         <v>394</v>
       </c>
       <c r="B395" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C395" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="C395" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="D395" s="5" t="s">
         <v>45</v>
@@ -7570,7 +7896,7 @@
         <v>83</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D396" s="5" t="s">
         <v>9</v>
@@ -7584,10 +7910,10 @@
         <v>93</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>280</v>
+        <v>459</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -7598,10 +7924,10 @@
         <v>116</v>
       </c>
       <c r="C398" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="D398" s="5" t="s">
         <v>402</v>
-      </c>
-      <c r="D398" s="5" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
@@ -7609,10 +7935,10 @@
         <v>398</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D399" s="5" t="s">
         <v>118</v>
@@ -7626,7 +7952,7 @@
         <v>91</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D400" s="5" t="s">
         <v>56</v>
@@ -7640,10 +7966,10 @@
         <v>93</v>
       </c>
       <c r="C401" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D401" s="5" t="s">
         <v>406</v>
-      </c>
-      <c r="D401" s="5" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -7654,10 +7980,10 @@
         <v>93</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D402" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -7668,10 +7994,10 @@
         <v>91</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="D403" s="5" t="s">
-        <v>260</v>
+        <v>408</v>
+      </c>
+      <c r="D403" s="5">
+        <v>124</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -7682,7 +8008,7 @@
         <v>83</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D404" s="5" t="s">
         <v>218</v>
@@ -7696,7 +8022,7 @@
         <v>83</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D405" s="5" t="s">
         <v>218</v>
@@ -7710,10 +8036,10 @@
         <v>116</v>
       </c>
       <c r="C406" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="D406" s="5" t="s">
         <v>412</v>
-      </c>
-      <c r="D406" s="5" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -7724,10 +8050,10 @@
         <v>93</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
@@ -7738,10 +8064,10 @@
         <v>116</v>
       </c>
       <c r="C408" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="D408" s="5" t="s">
         <v>415</v>
-      </c>
-      <c r="D408" s="5" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -7752,7 +8078,7 @@
         <v>103</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D409" s="5" t="s">
         <v>67</v>
@@ -7766,7 +8092,7 @@
         <v>116</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D410" s="5" t="s">
         <v>81</v>
@@ -7780,7 +8106,7 @@
         <v>93</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D411" s="5" t="s">
         <v>40</v>
@@ -7794,7 +8120,7 @@
         <v>305</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D412" s="5" t="s">
         <v>199</v>
@@ -7808,7 +8134,7 @@
         <v>305</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D413" s="5" t="s">
         <v>199</v>
@@ -7819,13 +8145,13 @@
         <v>413</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -7847,10 +8173,10 @@
         <v>415</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D416" s="5">
         <v>82</v>
@@ -7878,7 +8204,7 @@
         <v>113</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D418" s="5">
         <v>81</v>
@@ -7892,7 +8218,7 @@
         <v>240</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D419" s="5">
         <v>67</v>
@@ -7906,7 +8232,7 @@
         <v>111</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D420" s="5">
         <v>130</v>
@@ -7920,7 +8246,7 @@
         <v>111</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D421" s="5">
         <v>67</v>
@@ -7934,7 +8260,7 @@
         <v>91</v>
       </c>
       <c r="C422" s="21" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D422" s="22" t="s">
         <v>56</v>
@@ -7962,7 +8288,7 @@
         <v>91</v>
       </c>
       <c r="C424" s="21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D424" s="22" t="s">
         <v>56</v>
@@ -7976,7 +8302,7 @@
         <v>4</v>
       </c>
       <c r="C425" s="21" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D425" s="22" t="s">
         <v>218</v>
@@ -7990,7 +8316,7 @@
         <v>113</v>
       </c>
       <c r="C426" s="21" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D426" s="22" t="s">
         <v>45</v>
@@ -8004,7 +8330,7 @@
         <v>113</v>
       </c>
       <c r="C427" s="21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D427" s="22" t="s">
         <v>45</v>
@@ -8015,7 +8341,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C428" s="21" t="s">
         <v>8</v>
@@ -8029,10 +8355,10 @@
         <v>428</v>
       </c>
       <c r="B429" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C429" s="21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D429" s="22" t="s">
         <v>9</v>
@@ -8046,7 +8372,7 @@
         <v>91</v>
       </c>
       <c r="C430" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D430" s="22" t="s">
         <v>61</v>
@@ -8060,7 +8386,7 @@
         <v>93</v>
       </c>
       <c r="C431" s="21" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D431" s="22" t="s">
         <v>54</v>
@@ -8074,7 +8400,7 @@
         <v>246</v>
       </c>
       <c r="C432" s="21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D432" s="22" t="s">
         <v>56</v>
@@ -8085,7 +8411,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C433" s="21" t="s">
         <v>102</v>
@@ -8099,7 +8425,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C434" s="21" t="s">
         <v>34</v>
@@ -8116,7 +8442,7 @@
         <v>50</v>
       </c>
       <c r="C435" s="21" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D435" s="22" t="s">
         <v>195</v>
@@ -8127,13 +8453,13 @@
         <v>435</v>
       </c>
       <c r="B436" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="C436" s="21" t="s">
         <v>437</v>
       </c>
-      <c r="C436" s="21" t="s">
+      <c r="D436" s="22" t="s">
         <v>438</v>
-      </c>
-      <c r="D436" s="22" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
@@ -8148,6 +8474,1280 @@
       </c>
       <c r="D437" s="22">
         <v>313</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A438" s="20">
+        <v>437</v>
+      </c>
+      <c r="B438" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C438" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="D438" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A439" s="20">
+        <v>438</v>
+      </c>
+      <c r="B439" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C439" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="D439" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A440" s="20">
+        <v>439</v>
+      </c>
+      <c r="B440" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="C440" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="D440" s="22">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A441" s="20">
+        <v>440</v>
+      </c>
+      <c r="B441" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C441" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="D441" s="22">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A442" s="20">
+        <v>441</v>
+      </c>
+      <c r="B442" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C442" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="D442" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A443" s="20">
+        <v>442</v>
+      </c>
+      <c r="B443" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C443" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="D443" s="22">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A444" s="20">
+        <v>443</v>
+      </c>
+      <c r="B444" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C444" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="D444" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A445" s="20">
+        <v>444</v>
+      </c>
+      <c r="B445" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C445" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="D445" s="24">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A446" s="20">
+        <v>445</v>
+      </c>
+      <c r="B446" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C446" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="D446" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A447" s="20">
+        <v>446</v>
+      </c>
+      <c r="B447" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C447" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D447" s="22">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A448" s="20">
+        <v>447</v>
+      </c>
+      <c r="B448" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C448" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="D448" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A449" s="20">
+        <v>448</v>
+      </c>
+      <c r="B449" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C449" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="D449" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450" s="20">
+        <v>449</v>
+      </c>
+      <c r="B450" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C450" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="D450" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A451" s="20">
+        <v>450</v>
+      </c>
+      <c r="B451" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C451" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D451" s="22">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A452" s="20">
+        <v>451</v>
+      </c>
+      <c r="B452" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="C452" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D452" s="22">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A453" s="20">
+        <v>452</v>
+      </c>
+      <c r="B453" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C453" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D453" s="22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A454" s="20">
+        <v>453</v>
+      </c>
+      <c r="B454" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C454" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D454" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A455" s="20">
+        <v>454</v>
+      </c>
+      <c r="B455" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C455" s="21" t="s">
+        <v>449</v>
+      </c>
+      <c r="D455" s="22">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A456" s="20">
+        <v>455</v>
+      </c>
+      <c r="B456" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C456" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="D456" s="22">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A457" s="20">
+        <v>456</v>
+      </c>
+      <c r="B457" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C457" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="D457" s="22" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A458" s="20">
+        <v>457</v>
+      </c>
+      <c r="B458" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C458" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D458" s="22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A459" s="20">
+        <v>458</v>
+      </c>
+      <c r="B459" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C459" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="D459" s="22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A460" s="20">
+        <v>459</v>
+      </c>
+      <c r="B460" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C460" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="D460" s="22">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A461" s="20">
+        <v>460</v>
+      </c>
+      <c r="B461" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C461" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="D461" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A462" s="20">
+        <v>461</v>
+      </c>
+      <c r="B462" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C462" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="D462" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A463" s="20">
+        <v>462</v>
+      </c>
+      <c r="B463" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C463" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="D463" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A464" s="20">
+        <v>463</v>
+      </c>
+      <c r="B464" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="C464" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="D464" s="22" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A465" s="20">
+        <v>464</v>
+      </c>
+      <c r="B465" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C465" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="D465" s="22" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A466" s="20">
+        <v>465</v>
+      </c>
+      <c r="B466" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C466" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="D466" s="22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A467" s="20">
+        <v>466</v>
+      </c>
+      <c r="B467" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="C467" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="D467" s="22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A468" s="20">
+        <v>467</v>
+      </c>
+      <c r="B468" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C468" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="D468" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A469" s="20">
+        <v>468</v>
+      </c>
+      <c r="B469" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C469" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="D469" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A470" s="20">
+        <v>469</v>
+      </c>
+      <c r="B470" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C470" s="21" t="s">
+        <v>462</v>
+      </c>
+      <c r="D470" s="22" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A471" s="20">
+        <v>470</v>
+      </c>
+      <c r="B471" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C471" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="D471" s="22" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A472" s="20">
+        <v>471</v>
+      </c>
+      <c r="B472" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C472" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="D472" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A473" s="20">
+        <v>472</v>
+      </c>
+      <c r="B473" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="C473" s="21" t="s">
+        <v>466</v>
+      </c>
+      <c r="D473" s="22" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A474" s="20">
+        <v>473</v>
+      </c>
+      <c r="B474" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="C474" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="D474" s="22" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A475" s="20">
+        <v>474</v>
+      </c>
+      <c r="B475" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C475" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="D475" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A476" s="20">
+        <v>475</v>
+      </c>
+      <c r="B476" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C476" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="D476" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A477" s="20">
+        <v>476</v>
+      </c>
+      <c r="B477" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C477" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="D477" s="22" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A478" s="20">
+        <v>477</v>
+      </c>
+      <c r="B478" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C478" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="D478" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A479" s="20">
+        <v>478</v>
+      </c>
+      <c r="B479" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C479" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="D479" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A480" s="20">
+        <v>479</v>
+      </c>
+      <c r="B480" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C480" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="D480" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A481" s="20">
+        <v>480</v>
+      </c>
+      <c r="B481" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C481" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="D481" s="22" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A482" s="20">
+        <v>481</v>
+      </c>
+      <c r="B482" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C482" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="D482" s="22" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A483" s="20">
+        <v>482</v>
+      </c>
+      <c r="B483" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C483" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="D483" s="22" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A484" s="20">
+        <v>483</v>
+      </c>
+      <c r="B484" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C484" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="D484" s="22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A485" s="20">
+        <v>484</v>
+      </c>
+      <c r="B485" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C485" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="D485" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A486" s="20">
+        <v>485</v>
+      </c>
+      <c r="B486" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C486" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="D486" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A487" s="20">
+        <v>486</v>
+      </c>
+      <c r="B487" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="C487" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D487" s="22" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A488" s="20">
+        <v>487</v>
+      </c>
+      <c r="B488" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C488" s="21" t="s">
+        <v>486</v>
+      </c>
+      <c r="D488" s="22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A489" s="20">
+        <v>488</v>
+      </c>
+      <c r="B489" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C489" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D489" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A490" s="20">
+        <v>489</v>
+      </c>
+      <c r="B490" s="21" t="s">
+        <v>487</v>
+      </c>
+      <c r="C490" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="D490" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A491" s="20">
+        <v>490</v>
+      </c>
+      <c r="B491" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C491" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="D491" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A492" s="20">
+        <v>491</v>
+      </c>
+      <c r="B492" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C492" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D492" s="22" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A493" s="20">
+        <v>492</v>
+      </c>
+      <c r="B493" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C493" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="D493" s="22" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A494" s="20">
+        <v>493</v>
+      </c>
+      <c r="B494" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C494" s="21" t="s">
+        <v>466</v>
+      </c>
+      <c r="D494" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A495" s="20">
+        <v>494</v>
+      </c>
+      <c r="B495" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C495" s="21" t="s">
+        <v>493</v>
+      </c>
+      <c r="D495" s="22" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A496" s="20">
+        <v>495</v>
+      </c>
+      <c r="B496" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C496" s="21" t="s">
+        <v>494</v>
+      </c>
+      <c r="D496" s="22" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A497" s="20">
+        <v>496</v>
+      </c>
+      <c r="B497" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C497" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D497" s="22" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A498" s="20">
+        <v>497</v>
+      </c>
+      <c r="B498" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C498" s="21" t="s">
+        <v>495</v>
+      </c>
+      <c r="D498" s="22" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A499" s="20">
+        <v>498</v>
+      </c>
+      <c r="B499" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C499" s="21" t="s">
+        <v>496</v>
+      </c>
+      <c r="D499" s="22" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500" s="20">
+        <v>499</v>
+      </c>
+      <c r="B500" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C500" s="21" t="s">
+        <v>498</v>
+      </c>
+      <c r="D500" s="22" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501" s="20">
+        <v>500</v>
+      </c>
+      <c r="B501" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C501" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="D501" s="22">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502" s="20">
+        <v>501</v>
+      </c>
+      <c r="B502" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C502" s="21" t="s">
+        <v>501</v>
+      </c>
+      <c r="D502" s="22">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503" s="20">
+        <v>502</v>
+      </c>
+      <c r="B503" s="21" t="s">
+        <v>502</v>
+      </c>
+      <c r="C503" s="21" t="s">
+        <v>503</v>
+      </c>
+      <c r="D503" s="22" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504" s="20">
+        <v>503</v>
+      </c>
+      <c r="B504" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C504" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="D504" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505" s="20">
+        <v>504</v>
+      </c>
+      <c r="B505" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C505" s="21" t="s">
+        <v>506</v>
+      </c>
+      <c r="D505" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506" s="20">
+        <v>505</v>
+      </c>
+      <c r="B506" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C506" s="21" t="s">
+        <v>507</v>
+      </c>
+      <c r="D506" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A507" s="20">
+        <v>506</v>
+      </c>
+      <c r="B507" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C507" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="D507" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A508" s="20">
+        <v>507</v>
+      </c>
+      <c r="B508" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C508" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="D508" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A509" s="20">
+        <v>508</v>
+      </c>
+      <c r="B509" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C509" s="21" t="s">
+        <v>509</v>
+      </c>
+      <c r="D509" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A510" s="20">
+        <v>509</v>
+      </c>
+      <c r="B510" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="C510" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="D510" s="22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A511" s="20">
+        <v>510</v>
+      </c>
+      <c r="B511" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="C511" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="D511" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A512" s="20">
+        <v>511</v>
+      </c>
+      <c r="B512" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C512" s="21" t="s">
+        <v>511</v>
+      </c>
+      <c r="D512" s="22">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A513" s="20">
+        <v>512</v>
+      </c>
+      <c r="B513" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C513" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="D513" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A514" s="20">
+        <v>513</v>
+      </c>
+      <c r="B514" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C514" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="D514" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A515" s="20">
+        <v>514</v>
+      </c>
+      <c r="B515" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C515" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="D515" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A516" s="25">
+        <v>515</v>
+      </c>
+      <c r="B516" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C516" s="26" t="s">
+        <v>513</v>
+      </c>
+      <c r="D516" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A517" s="20">
+        <v>516</v>
+      </c>
+      <c r="B517" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C517" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="D517" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A518" s="20">
+        <v>517</v>
+      </c>
+      <c r="B518" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C518" s="21" t="s">
+        <v>515</v>
+      </c>
+      <c r="D518" s="22">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A519" s="20">
+        <v>518</v>
+      </c>
+      <c r="B519" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C519" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="D519" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A520" s="20">
+        <v>519</v>
+      </c>
+      <c r="B520" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C520" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="D520" s="22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A521" s="20">
+        <v>520</v>
+      </c>
+      <c r="B521" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C521" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="D521" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A522" s="20">
+        <v>521</v>
+      </c>
+      <c r="B522" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C522" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D522" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A523" s="20">
+        <v>522</v>
+      </c>
+      <c r="B523" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C523" s="21" t="s">
+        <v>517</v>
+      </c>
+      <c r="D523" s="22">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A524" s="20">
+        <v>523</v>
+      </c>
+      <c r="B524" s="21" t="s">
+        <v>518</v>
+      </c>
+      <c r="C524" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="D524" s="22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A525" s="20">
+        <v>524</v>
+      </c>
+      <c r="B525" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C525" s="21" t="s">
+        <v>519</v>
+      </c>
+      <c r="D525" s="22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A526" s="20">
+        <v>525</v>
+      </c>
+      <c r="B526" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C526" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D526" s="22" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A527" s="28">
+        <v>526</v>
+      </c>
+      <c r="B527" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C527" s="29" t="s">
+        <v>520</v>
+      </c>
+      <c r="D527" s="30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A528" s="28">
+        <v>527</v>
+      </c>
+      <c r="B528" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="C528" s="29" t="s">
+        <v>521</v>
+      </c>
+      <c r="D528" s="30">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/COST.xlsx
+++ b/COST.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38C798D6-8780-4836-BB4A-1EF7E31E707D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EE0D692-F7BE-4FD1-82C4-2C7AB8BBAD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COST" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="537">
   <si>
     <t>S.No</t>
   </si>
@@ -1586,6 +1586,51 @@
   </si>
   <si>
     <t>GSPE MOULDING ASSY-SIDE SILL,LH</t>
+  </si>
+  <si>
+    <t>DEFOSTER RR LHD</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR LH STD AI3 ; SHIELD COVER FRT SEAT OTR RH H/ADJ AI3 NBY</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR LH STD AI3 ; SHIELD COVER FRT SEAT OTR RH H/ADJ AI3 T9Y</t>
+  </si>
+  <si>
+    <t>S/COVER FRT SEAT OTR LH MNL ;  S/COVER FRT CUSH OTR RH MNL H/ADJ RHD YGN</t>
+  </si>
+  <si>
+    <t>HOUSING BN7I DRL PSTN LH ; HOUSING BN7I DRL PSTN RH</t>
+  </si>
+  <si>
+    <t>KNOB ASSY-FRT SEAT H/ADJ,RH</t>
+  </si>
+  <si>
+    <t>KNOB FR SEAT RECL LH</t>
+  </si>
+  <si>
+    <t>DR-PASSANGER AIR BAG RHD</t>
+  </si>
+  <si>
+    <t>DR-PASSANGER AIR BAG LHD</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>SHIELD COVER FRT SEAT OTR LH STD AI3 ; SHIELD COVER FRT SEAT OTR RH H/ADJ AI3</t>
+  </si>
+  <si>
+    <t>SIDE SILL LH-QXIL ; SIDE SILL RH-QXIR</t>
+  </si>
+  <si>
+    <t>SIDE SILL LH-QXIL</t>
   </si>
 </sst>
 </file>
@@ -2070,8 +2115,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:D528" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D528" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:D542" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D542" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D56">
     <sortCondition ref="C1:C56"/>
   </sortState>
@@ -2348,7 +2393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D528"/>
+  <dimension ref="A1:D542"/>
   <sheetFormatPr defaultColWidth="52.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -2732,8 +2777,8 @@
       <c r="C27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>43</v>
+      <c r="D27" s="3">
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -4664,8 +4709,8 @@
       <c r="C165" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D165" s="5">
-        <v>82</v>
+      <c r="D165" s="5" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -6988,8 +7033,8 @@
       <c r="C331" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D331" s="5" t="s">
-        <v>161</v>
+      <c r="D331" s="5">
+        <v>22</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -9748,6 +9793,202 @@
       </c>
       <c r="D528" s="30">
         <v>123</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A529" s="20">
+        <v>528</v>
+      </c>
+      <c r="B529" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C529" s="21" t="s">
+        <v>522</v>
+      </c>
+      <c r="D529" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A530" s="20">
+        <v>529</v>
+      </c>
+      <c r="B530" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C530" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D530" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A531" s="20">
+        <v>530</v>
+      </c>
+      <c r="B531" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C531" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="D531" s="22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A532" s="20">
+        <v>531</v>
+      </c>
+      <c r="B532" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C532" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D532" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A533" s="20">
+        <v>532</v>
+      </c>
+      <c r="B533" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C533" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="D533" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A534" s="20">
+        <v>533</v>
+      </c>
+      <c r="B534" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C534" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="D534" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A535" s="20">
+        <v>534</v>
+      </c>
+      <c r="B535" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C535" s="21" t="s">
+        <v>528</v>
+      </c>
+      <c r="D535" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A536" s="20">
+        <v>535</v>
+      </c>
+      <c r="B536" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C536" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="D536" s="22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A537" s="20">
+        <v>536</v>
+      </c>
+      <c r="B537" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="C537" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="D537" s="22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A538" s="20">
+        <v>537</v>
+      </c>
+      <c r="B538" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C538" s="21" t="s">
+        <v>531</v>
+      </c>
+      <c r="D538" s="22" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A539" s="20">
+        <v>538</v>
+      </c>
+      <c r="B539" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C539" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="D539" s="22" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A540" s="20">
+        <v>539</v>
+      </c>
+      <c r="B540" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C540" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="D540" s="22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A541" s="20">
+        <v>540</v>
+      </c>
+      <c r="B541" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C541" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="D541" s="22" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A542" s="20">
+        <v>541</v>
+      </c>
+      <c r="B542" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C542" s="21" t="s">
+        <v>536</v>
+      </c>
+      <c r="D542" s="22">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
